--- a/docentes/Medina Tolentino Elio - Estadisticos 20211.xlsx
+++ b/docentes/Medina Tolentino Elio - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="22">
   <si>
     <t>Mat</t>
   </si>
@@ -76,52 +76,13 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>TZANAHUA</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>TREJO</t>
-  </si>
-  <si>
-    <t>CUAHUA</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>GALEOTE</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>LUENGAS</t>
-  </si>
-  <si>
-    <t>ERICA</t>
-  </si>
-  <si>
-    <t>JAVIER FERNANDO</t>
-  </si>
-  <si>
-    <t>ALEXIS</t>
-  </si>
-  <si>
-    <t>JOCELYN BERENICE</t>
-  </si>
-  <si>
-    <t>JELIN JANET</t>
-  </si>
-  <si>
-    <t>ELIZABETH</t>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
+    <t>ELIDETH</t>
   </si>
 </sst>
 </file>
@@ -639,16 +600,19 @@
         <v>38</v>
       </c>
       <c r="D2">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>78.95</v>
+      </c>
+      <c r="H2">
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -662,16 +626,19 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>75.76000000000001</v>
+      </c>
+      <c r="H3">
+        <v>5.8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -685,16 +652,19 @@
         <v>33</v>
       </c>
       <c r="D4">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>69.7</v>
+      </c>
+      <c r="H4">
+        <v>6.4</v>
       </c>
     </row>
   </sheetData>
@@ -750,16 +720,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G2">
-        <v>73.68000000000001</v>
+        <v>78.95</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -776,16 +746,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G3">
-        <v>60.61</v>
+        <v>75.76000000000001</v>
       </c>
       <c r="H3">
-        <v>5.8</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -802,16 +772,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F4">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G4">
-        <v>57.58</v>
+        <v>69.7</v>
       </c>
       <c r="H4">
-        <v>6.4</v>
+        <v>7.1</v>
       </c>
     </row>
   </sheetData>
@@ -821,7 +791,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -853,140 +823,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920256</v>
+        <v>19330051920024</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G2">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>19330051920258</v>
-      </c>
-      <c r="B3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>19330051920257</v>
-      </c>
-      <c r="B4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>19330051920035</v>
-      </c>
-      <c r="B5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>19330051920348</v>
-      </c>
-      <c r="B6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" t="s">
-        <v>33</v>
-      </c>
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>19330051920414</v>
-      </c>
-      <c r="B7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7" t="s">
-        <v>34</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Medina Tolentino Elio - Estadisticos 20211.xlsx
+++ b/docentes/Medina Tolentino Elio - Estadisticos 20211.xlsx
@@ -76,13 +76,13 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>ELIDETH</t>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>BERISTAIN</t>
+  </si>
+  <si>
+    <t>LUIS ENRIQUE</t>
   </si>
 </sst>
 </file>
@@ -720,16 +720,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G2">
-        <v>78.95</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="H2">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -746,16 +746,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="G3">
-        <v>75.76000000000001</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>6.9</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -772,16 +772,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="G4">
-        <v>69.7</v>
+        <v>100</v>
       </c>
       <c r="H4">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
     </row>
   </sheetData>
@@ -823,7 +823,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920024</v>
+        <v>19330051920014</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
